--- a/data/trans_orig/P80_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P80_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>497835</t>
+          <t>540500</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>489936</t>
+          <t>531196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>501680</t>
+          <t>545733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>437463</t>
+          <t>478675</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>430422</t>
+          <t>471454</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>441922</t>
+          <t>482523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>935298</t>
+          <t>1019175</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>926240</t>
+          <t>1007103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>941159</t>
+          <t>1025727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>979</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>443062</t>
+          <t>473251</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>435305</t>
+          <t>463954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>447572</t>
+          <t>477603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>371866</t>
+          <t>411243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>363237</t>
+          <t>402598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>376948</t>
+          <t>416939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>814928</t>
+          <t>884494</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>805424</t>
+          <t>873634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>822566</t>
+          <t>891818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,27 +2089,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>667286</t>
+          <t>470510</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>662049</t>
+          <t>466030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>164750</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159724</t>
+          <t>178287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166584</t>
+          <t>186763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>832036</t>
+          <t>654530</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826858</t>
+          <t>648616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>834943</t>
+          <t>657642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1003914</t>
+          <t>1097648</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>986932</t>
+          <t>1082540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1015315</t>
+          <t>1109360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>964825</t>
+          <t>846285</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>955804</t>
+          <t>837965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>971359</t>
+          <t>851143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1968738</t>
+          <t>1943933</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1950012</t>
+          <t>1926707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1983460</t>
+          <t>1957686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>37632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>461567</t>
+          <t>549313</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>450872</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>467330</t>
+          <t>557253</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>829778</t>
+          <t>817230</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>822666</t>
+          <t>809478</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>834205</t>
+          <t>822389</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1291344</t>
+          <t>1366543</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1279264</t>
+          <t>1350823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1298686</t>
+          <t>1376940</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>680</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,17 +3975,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>230634</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>218054</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>235509</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>220913</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>240320</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,27 +4170,27 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>758523</t>
+          <t>841207</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>755131</t>
+          <t>837713</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>759907</t>
+          <t>842674</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>994033</t>
+          <t>1071840</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>981656</t>
+          <t>1060087</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>998789</t>
+          <t>1077828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>616</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>758</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>758</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3309173</t>
+          <t>3361855</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3286153</t>
+          <t>3338163</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3327627</t>
+          <t>3380460</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3527204</t>
+          <t>3578661</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3512707</t>
+          <t>3564552</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3539238</t>
+          <t>3590884</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6836377</t>
+          <t>6940515</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6807011</t>
+          <t>6913720</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6857243</t>
+          <t>6963047</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>55680</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>28371</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>45037</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>74913</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>49784</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>8805</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>24228</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>31210</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
